--- a/artfynd/A 51037-2025 artfynd.xlsx
+++ b/artfynd/A 51037-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117865419</v>
+        <v>117865422</v>
       </c>
       <c r="B2" t="n">
-        <v>97744</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117865416</v>
+        <v>117865418</v>
       </c>
       <c r="B3" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +813,7 @@
         <v>7009892</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117865418</v>
+        <v>117865428</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,12 +969,7 @@
         <v>117865421</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,37 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117865428</v>
+        <v>117865419</v>
       </c>
       <c r="B6" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,37 +1169,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117865415</v>
+        <v>117865416</v>
       </c>
       <c r="B7" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,12 +1269,7 @@
         <v>117865417</v>
       </c>
       <c r="B8" t="n">
-        <v>104919</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,108 +1360,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>117865422</v>
-      </c>
-      <c r="B9" t="n">
-        <v>90786</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>658</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Storklinsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>552680</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7009892</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51037-2025 artfynd.xlsx
+++ b/artfynd/A 51037-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865428</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865421</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865419</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865416</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,8 +1395,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117865417</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>